--- a/订货商品汇总看板_格式化模板.xlsx
+++ b/订货商品汇总看板_格式化模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wadec\Documents\projects\mainyan-auto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4373E19E-25CF-4FFE-8C95-12335B9B7824}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B48E0E53-4830-4FD1-9E11-928D28A77453}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,15 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$7:$C$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$7:$C$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">Sheet1!$1:$7</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>麦安研门店下单统计表</t>
   </si>
@@ -40,6 +41,12 @@
     <t>运费金额</t>
   </si>
   <si>
+    <t>下单：2026.05.25</t>
+  </si>
+  <si>
+    <t>配送：2026.05.27</t>
+  </si>
+  <si>
     <t>合计下单金额</t>
   </si>
   <si>
@@ -58,33 +65,34 @@
     <t>单位</t>
   </si>
   <si>
-    <t>合计数量</t>
-  </si>
-  <si>
-    <t>公版包材类</t>
-  </si>
-  <si>
-    <t>K102烘焙圆形锡纸托</t>
-  </si>
-  <si>
-    <t>200张/包</t>
-  </si>
-  <si>
-    <t>包</t>
-  </si>
-  <si>
-    <t>加厚大号裱花袋</t>
-  </si>
-  <si>
-    <t>100个/包 长约38cm</t>
-  </si>
-  <si>
-    <t>配送：2026.05.24</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>下单：2026.05.22</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>合计</t>
+  </si>
+  <si>
+    <t>东站宝泰店</t>
+  </si>
+  <si>
+    <t>冷冻面团</t>
+  </si>
+  <si>
+    <t>帝王榴莲面团</t>
+  </si>
+  <si>
+    <t>约200g/个 12个/包</t>
+  </si>
+  <si>
+    <t>个</t>
+  </si>
+  <si>
+    <t>配送费</t>
+  </si>
+  <si>
+    <t>冷链运费(拍后发货)</t>
+  </si>
+  <si>
+    <t>按趟收费</t>
+  </si>
+  <si>
+    <t>趟</t>
   </si>
 </sst>
 </file>
@@ -92,12 +100,38 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="0.00_ "/>
+    <numFmt numFmtId="178" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
@@ -106,35 +140,19 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="16"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
+      <sz val="8"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -142,13 +160,12 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -178,7 +195,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -190,7 +207,9 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top style="thin">
         <color auto="1"/>
       </top>
@@ -212,66 +231,54 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="178" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -611,175 +618,174 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="4.8984375" style="8" customWidth="1"/>
-    <col min="2" max="2" width="13.69921875" style="8" customWidth="1"/>
-    <col min="3" max="3" width="22" style="8" customWidth="1"/>
-    <col min="4" max="4" width="19.59765625" style="8" customWidth="1"/>
-    <col min="5" max="5" width="5.09765625" style="10" customWidth="1"/>
-    <col min="6" max="6" width="9.796875" style="11" customWidth="1"/>
-    <col min="7" max="7" width="9" style="11" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="8"/>
+    <col min="1" max="1" width="4.3984375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="9.8984375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="18.3984375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="4.3984375" style="4" customWidth="1"/>
+    <col min="6" max="6" width="6.5" style="5" customWidth="1"/>
+    <col min="7" max="7" width="9" style="5" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" ht="23.4" x14ac:dyDescent="0.5">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
+    <row r="1" spans="1:7" s="1" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A1" s="6"/>
+      <c r="B1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
     </row>
-    <row r="2" spans="1:7" s="3" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D2" s="14" t="s">
+    <row r="2" spans="1:7" s="2" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="15"/>
-      <c r="F2" s="12">
+      <c r="E2" s="18"/>
+      <c r="F2" s="7">
         <f>SUM(G2:G2)</f>
         <v>0</v>
       </c>
-      <c r="G2" s="13">
+      <c r="G2" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="3" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D3" s="14" t="s">
+    <row r="3" spans="1:7" s="2" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D3" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="15"/>
-      <c r="F3" s="12">
+      <c r="E3" s="18"/>
+      <c r="F3" s="7">
         <f>SUM(G3:G3)</f>
         <v>0</v>
       </c>
-      <c r="G3" s="13">
+      <c r="G3" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" s="3" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D4" s="14" t="s">
+    <row r="4" spans="1:7" s="2" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D4" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="15"/>
-      <c r="F4" s="12">
+      <c r="E4" s="18"/>
+      <c r="F4" s="7">
         <f>SUM(G4:G4)</f>
         <v>0</v>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" s="3" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D5" s="14" t="s">
+    <row r="5" spans="1:7" s="2" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D5" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="15"/>
-      <c r="F5" s="12">
+      <c r="E5" s="18"/>
+      <c r="F5" s="7">
         <f>SUM(G5:G5)</f>
         <v>0</v>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" s="3" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="14" t="s">
+    <row r="6" spans="1:7" s="2" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="15"/>
-      <c r="F6" s="12">
+      <c r="B6" s="10"/>
+      <c r="C6" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="18"/>
+      <c r="F6" s="7">
         <f>SUM(G6:G6)</f>
         <v>0</v>
       </c>
-      <c r="G6" s="13">
-        <f t="shared" ref="G6" si="0">SUM(G2:G5)</f>
+      <c r="G6" s="8">
+        <f>SUM(G2:G5)</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="22.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="5" t="s">
+      <c r="A7" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="B7" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="C7" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="D7" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="5"/>
+      <c r="E7" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="8" spans="1:7" ht="22.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="9">
-        <f>ROW()-7</f>
+    <row r="8" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="15">
+        <f t="shared" ref="A8" si="0">ROW()-7</f>
         <v>1</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="9" t="s">
+      <c r="B8" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="4">
-        <v>4</v>
-      </c>
-      <c r="G8" s="4"/>
+      <c r="C8" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" s="12">
+        <v>36</v>
+      </c>
+      <c r="G8" s="12">
+        <v>24</v>
+      </c>
     </row>
-    <row r="9" spans="1:7" ht="22.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="9">
+    <row r="9" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="15">
         <f t="shared" ref="A9" si="1">ROW()-7</f>
         <v>2</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F9" s="4">
-        <v>2</v>
-      </c>
-      <c r="G9" s="4"/>
+      <c r="B9" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" s="12">
+        <v>1</v>
+      </c>
+      <c r="G9" s="12"/>
     </row>
-    <row r="10" spans="1:7" ht="22.95" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="11" spans="1:7" ht="22.95" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="12" spans="1:7" ht="22.95" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="13" spans="1:7" ht="22.95" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="14" spans="1:7" ht="22.95" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="15" spans="1:7" ht="22.95" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
-  <autoFilter ref="A7:C7" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A7:C9" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="5">
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="D3:E3"/>
@@ -787,8 +793,11 @@
     <mergeCell ref="D5:E5"/>
     <mergeCell ref="D6:E6"/>
   </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.156944444444444" right="0.156944444444444" top="0.27500000000000002" bottom="1" header="0.196527777777778" footer="0.5"/>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <pageMargins left="0.156944444444444" right="0.156944444444444" top="0.27500000000000002" bottom="0.118055555555556" header="0.196527777777778" footer="0.23611111111111099"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter>
+    <oddFooter>&amp;R第 &amp;P 页，共 &amp;N 页</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
--- a/订货商品汇总看板_格式化模板.xlsx
+++ b/订货商品汇总看板_格式化模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wadec\Documents\projects\mainyan-auto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B48E0E53-4830-4FD1-9E11-928D28A77453}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54FEB9B0-BE2D-438A-A349-2002F396B19A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -99,8 +99,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="178" formatCode="0.00_ "/>
+  <numFmts count="2">
+    <numFmt numFmtId="176" formatCode="0.00_ "/>
+    <numFmt numFmtId="177" formatCode="0_ "/>
   </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
@@ -111,27 +112,32 @@
     <font>
       <sz val="16"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -142,17 +148,20 @@
     <font>
       <sz val="8"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -160,12 +169,14 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -235,7 +246,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -252,7 +263,7 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -279,6 +290,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -755,10 +769,10 @@
       <c r="E8" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="19">
         <v>36</v>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="19">
         <v>24</v>
       </c>
     </row>
@@ -779,10 +793,10 @@
       <c r="E9" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="F9" s="12">
+      <c r="F9" s="19">
         <v>1</v>
       </c>
-      <c r="G9" s="12"/>
+      <c r="G9" s="19"/>
     </row>
   </sheetData>
   <autoFilter ref="A7:C9" xr:uid="{00000000-0009-0000-0000-000000000000}"/>

--- a/订货商品汇总看板_格式化模板.xlsx
+++ b/订货商品汇总看板_格式化模板.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wadec\Documents\projects\mainyan-auto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54FEB9B0-BE2D-438A-A349-2002F396B19A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66DCE286-5408-4F3A-8D97-25FAAA107903}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -44,55 +44,56 @@
     <t>下单：2026.05.25</t>
   </si>
   <si>
+    <t>合计下单金额</t>
+  </si>
+  <si>
+    <t>序号</t>
+  </si>
+  <si>
+    <t>商品分类</t>
+  </si>
+  <si>
+    <t>商品名称</t>
+  </si>
+  <si>
+    <t>规格</t>
+  </si>
+  <si>
+    <t>单位</t>
+  </si>
+  <si>
+    <t>合计</t>
+  </si>
+  <si>
+    <t>东站宝泰店</t>
+  </si>
+  <si>
+    <t>冷冻面团</t>
+  </si>
+  <si>
+    <t>帝王榴莲面团</t>
+  </si>
+  <si>
+    <t>约200g/个 12个/包</t>
+  </si>
+  <si>
+    <t>个</t>
+  </si>
+  <si>
+    <t>配送费</t>
+  </si>
+  <si>
+    <t>冷链运费(拍后发货)</t>
+  </si>
+  <si>
+    <t>按趟收费</t>
+  </si>
+  <si>
+    <t>趟</t>
+  </si>
+  <si>
     <t>配送：2026.05.27</t>
-  </si>
-  <si>
-    <t>合计下单金额</t>
-  </si>
-  <si>
-    <t>序号</t>
-  </si>
-  <si>
-    <t>商品分类</t>
-  </si>
-  <si>
-    <t>商品名称</t>
-  </si>
-  <si>
-    <t>规格</t>
-  </si>
-  <si>
-    <t>单位</t>
-  </si>
-  <si>
-    <t>合计</t>
-  </si>
-  <si>
-    <t>东站宝泰店</t>
-  </si>
-  <si>
-    <t>冷冻面团</t>
-  </si>
-  <si>
-    <t>帝王榴莲面团</t>
-  </si>
-  <si>
-    <t>约200g/个 12个/包</t>
-  </si>
-  <si>
-    <t>个</t>
-  </si>
-  <si>
-    <t>配送费</t>
-  </si>
-  <si>
-    <t>冷链运费(拍后发货)</t>
-  </si>
-  <si>
-    <t>按趟收费</t>
-  </si>
-  <si>
-    <t>趟</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -286,13 +287,13 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="177" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="177" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -657,10 +658,10 @@
       <c r="G1" s="6"/>
     </row>
     <row r="2" spans="1:7" s="2" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="18"/>
+      <c r="E2" s="19"/>
       <c r="F2" s="7">
         <f>SUM(G2:G2)</f>
         <v>0</v>
@@ -670,10 +671,10 @@
       </c>
     </row>
     <row r="3" spans="1:7" s="2" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="18"/>
+      <c r="E3" s="19"/>
       <c r="F3" s="7">
         <f>SUM(G3:G3)</f>
         <v>0</v>
@@ -683,10 +684,10 @@
       </c>
     </row>
     <row r="4" spans="1:7" s="2" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D4" s="17" t="s">
+      <c r="D4" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="18"/>
+      <c r="E4" s="19"/>
       <c r="F4" s="7">
         <f>SUM(G4:G4)</f>
         <v>0</v>
@@ -696,10 +697,10 @@
       </c>
     </row>
     <row r="5" spans="1:7" s="2" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D5" s="17" t="s">
+      <c r="D5" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="18"/>
+      <c r="E5" s="19"/>
       <c r="F5" s="7">
         <f>SUM(G5:G5)</f>
         <v>0</v>
@@ -714,12 +715,12 @@
       </c>
       <c r="B6" s="10"/>
       <c r="C6" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="18"/>
+      <c r="E6" s="19"/>
       <c r="F6" s="7">
         <f>SUM(G6:G6)</f>
         <v>0</v>
@@ -731,25 +732,25 @@
     </row>
     <row r="7" spans="1:7" ht="22.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="C7" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="D7" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="E7" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="F7" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="G7" s="12" t="s">
         <v>13</v>
-      </c>
-      <c r="G7" s="12" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.4">
@@ -758,21 +759,21 @@
         <v>1</v>
       </c>
       <c r="B8" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="D8" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="E8" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="F8" s="19">
+      <c r="F8" s="17">
         <v>36</v>
       </c>
-      <c r="G8" s="19">
+      <c r="G8" s="17">
         <v>24</v>
       </c>
     </row>
@@ -782,21 +783,21 @@
         <v>2</v>
       </c>
       <c r="B9" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="D9" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="E9" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="E9" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="F9" s="19">
+      <c r="F9" s="17">
         <v>1</v>
       </c>
-      <c r="G9" s="19"/>
+      <c r="G9" s="17"/>
     </row>
   </sheetData>
   <autoFilter ref="A7:C9" xr:uid="{00000000-0009-0000-0000-000000000000}"/>

--- a/订货商品汇总看板_格式化模板.xlsx
+++ b/订货商品汇总看板_格式化模板.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wadec\Documents\projects\mainyan-auto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66DCE286-5408-4F3A-8D97-25FAAA107903}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A0BEEC2-551A-46C4-B304-69BCFFCC58A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -247,7 +247,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -294,6 +294,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -770,7 +773,7 @@
       <c r="E8" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="F8" s="17">
+      <c r="F8" s="20">
         <v>36</v>
       </c>
       <c r="G8" s="17">
@@ -794,7 +797,7 @@
       <c r="E9" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="F9" s="17">
+      <c r="F9" s="20">
         <v>1</v>
       </c>
       <c r="G9" s="17"/>

--- a/订货商品汇总看板_格式化模板.xlsx
+++ b/订货商品汇总看板_格式化模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wadec\Documents\projects\mainyan-auto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A0BEEC2-551A-46C4-B304-69BCFFCC58A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E676EB4F-95B7-444A-B0B2-8929FB3804EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -104,7 +104,7 @@
     <numFmt numFmtId="176" formatCode="0.00_ "/>
     <numFmt numFmtId="177" formatCode="0_ "/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <name val="Calibri"/>
@@ -175,6 +175,14 @@
     </font>
     <font>
       <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
       <family val="2"/>
@@ -287,14 +295,14 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="177" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="12" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -773,10 +781,10 @@
       <c r="E8" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="F8" s="20">
+      <c r="F8" s="17">
         <v>36</v>
       </c>
-      <c r="G8" s="17">
+      <c r="G8" s="20">
         <v>24</v>
       </c>
     </row>
@@ -797,10 +805,10 @@
       <c r="E9" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="F9" s="20">
+      <c r="F9" s="17">
         <v>1</v>
       </c>
-      <c r="G9" s="17"/>
+      <c r="G9" s="20"/>
     </row>
   </sheetData>
   <autoFilter ref="A7:C9" xr:uid="{00000000-0009-0000-0000-000000000000}"/>

--- a/订货商品汇总看板_格式化模板.xlsx
+++ b/订货商品汇总看板_格式化模板.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wadec\Documents\projects\mainyan-auto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E676EB4F-95B7-444A-B0B2-8929FB3804EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B71A5A9F-EE87-4046-94F4-AF2645798691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2064" yWindow="2208" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -104,7 +104,7 @@
     <numFmt numFmtId="176" formatCode="0.00_ "/>
     <numFmt numFmtId="177" formatCode="0_ "/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <name val="Calibri"/>
@@ -183,6 +183,14 @@
     <font>
       <b/>
       <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
       <family val="2"/>
@@ -255,7 +263,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -298,13 +306,16 @@
     <xf numFmtId="177" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="177" fontId="12" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="177" fontId="12" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -669,10 +680,10 @@
       <c r="G1" s="6"/>
     </row>
     <row r="2" spans="1:7" s="2" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="19"/>
+      <c r="E2" s="21"/>
       <c r="F2" s="7">
         <f>SUM(G2:G2)</f>
         <v>0</v>
@@ -682,10 +693,10 @@
       </c>
     </row>
     <row r="3" spans="1:7" s="2" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="19"/>
+      <c r="E3" s="21"/>
       <c r="F3" s="7">
         <f>SUM(G3:G3)</f>
         <v>0</v>
@@ -695,10 +706,10 @@
       </c>
     </row>
     <row r="4" spans="1:7" s="2" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="19"/>
+      <c r="E4" s="21"/>
       <c r="F4" s="7">
         <f>SUM(G4:G4)</f>
         <v>0</v>
@@ -708,10 +719,10 @@
       </c>
     </row>
     <row r="5" spans="1:7" s="2" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="19"/>
+      <c r="E5" s="21"/>
       <c r="F5" s="7">
         <f>SUM(G5:G5)</f>
         <v>0</v>
@@ -728,10 +739,10 @@
       <c r="C6" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="19"/>
+      <c r="E6" s="21"/>
       <c r="F6" s="7">
         <f>SUM(G6:G6)</f>
         <v>0</v>
@@ -772,7 +783,7 @@
       <c r="B8" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="19" t="s">
         <v>15</v>
       </c>
       <c r="D8" s="16" t="s">
@@ -784,7 +795,7 @@
       <c r="F8" s="17">
         <v>36</v>
       </c>
-      <c r="G8" s="20">
+      <c r="G8" s="18">
         <v>24</v>
       </c>
     </row>
@@ -796,7 +807,7 @@
       <c r="B9" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="19" t="s">
         <v>19</v>
       </c>
       <c r="D9" s="16" t="s">
@@ -808,7 +819,7 @@
       <c r="F9" s="17">
         <v>1</v>
       </c>
-      <c r="G9" s="20"/>
+      <c r="G9" s="18"/>
     </row>
   </sheetData>
   <autoFilter ref="A7:C9" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
